--- a/src/xlsx/dexEntry.xlsx
+++ b/src/xlsx/dexEntry.xlsx
@@ -1451,7 +1451,7 @@
       </c>
       <c r="C2" s="18" t="inlineStr">
         <is>
-          <t>妙蛙种子</t>
+          <t>妙蛙種子</t>
         </is>
       </c>
       <c r="D2" s="4" t="inlineStr">
@@ -1529,7 +1529,7 @@
       </c>
       <c r="S2" s="18" t="inlineStr">
         <is>
-          <t>背上的种子里储存着营养，所以即使好几天不吃东西也可以活得好好的！</t>
+          <t>背上的種子裡儲存著營養，所以即使好幾天不吃東西也可以活得好好的！</t>
         </is>
       </c>
     </row>
@@ -1617,7 +1617,7 @@
       </c>
       <c r="S3" s="18" t="inlineStr">
         <is>
-          <t>它的花苞会在吸收养分后长大。当花苞发出香味时，就预示着它快要开花了。</t>
+          <t>它的花苞會在吸收養分後長大。當花苞發出香味時，就預示著它快要開花了。</t>
         </is>
       </c>
     </row>
@@ -1705,7 +1705,7 @@
       </c>
       <c r="S4" s="18" t="inlineStr">
         <is>
-          <t>它背上开出的大花能够吸收太阳光并将其转换为能量。</t>
+          <t>它背上開出的大花能夠吸收太陽光並將其轉換為能量。</t>
         </is>
       </c>
     </row>
@@ -1715,7 +1715,7 @@
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>小火龙</t>
+          <t>小火龍</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
@@ -1793,7 +1793,7 @@
       </c>
       <c r="S5" s="18" t="inlineStr">
         <is>
-          <t>要是把它带到安静的地方，就能听到它的尾巴燃烧时发出的微小的声音。</t>
+          <t>要是把它帶到安靜的地方，就能聽到它的尾巴燃燒時發出的微小的聲音。</t>
         </is>
       </c>
     </row>
@@ -1803,7 +1803,7 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>火恐龙</t>
+          <t>火恐龍</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
@@ -1881,7 +1881,7 @@
       </c>
       <c r="S6" s="18" t="inlineStr">
         <is>
-          <t>在与强敌战斗的过程中，如果情绪变得兴奋起来，有时会喷出青白色的烈火。</t>
+          <t>在與強敵戰鬥的過程中，如果情緒變得興奮起來，有時會噴出青白色的烈火。</t>
         </is>
       </c>
     </row>
@@ -1891,7 +1891,7 @@
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>喷火龙</t>
+          <t>噴火龍</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
@@ -1969,7 +1969,7 @@
       </c>
       <c r="S7" s="4" t="inlineStr">
         <is>
-          <t>从口中喷出灼热的火焰时，尾巴尖端的红色火焰会燃烧得更加猛烈。</t>
+          <t>從口中噴出灼熱的火焰時，尾巴尖端的紅色火焰會燃燒得更加猛烈。</t>
         </is>
       </c>
     </row>
@@ -1979,7 +1979,7 @@
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>杰尼龟</t>
+          <t>傑尼龜</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
@@ -2057,7 +2057,7 @@
       </c>
       <c r="S8" s="4" t="inlineStr">
         <is>
-          <t>通过从水面喷水来捕食。在危急时刻会将四肢缩入龟壳里保护自己。</t>
+          <t>會從水面噴水捕食。危急時會將四肢縮入龜殼裡保護自己。</t>
         </is>
       </c>
     </row>
@@ -2067,7 +2067,7 @@
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>卡咪龟</t>
+          <t>卡咪龜</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
@@ -2145,7 +2145,7 @@
       </c>
       <c r="S9" s="4" t="inlineStr">
         <is>
-          <t>如果拍打它的头部，它会把头缩进壳里，但尾巴还是会露出来一点点。</t>
+          <t>如果拍打它的頭部，它會把頭縮進殼裡，但尾巴還是會露出來一點點。</t>
         </is>
       </c>
     </row>
@@ -2155,7 +2155,7 @@
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>水箭龟</t>
+          <t>水箭龜</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
@@ -2233,7 +2233,7 @@
       </c>
       <c r="S10" s="4" t="inlineStr">
         <is>
-          <t>一旦锁定了目标，它会以超越了消防水枪的力道来喷水。</t>
+          <t>一旦鎖定了目標，它會以超越了消防水槍的力道來噴水。</t>
         </is>
       </c>
     </row>
@@ -2243,7 +2243,7 @@
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>绿毛虫</t>
+          <t>綠毛蟲</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="S11" s="18" t="inlineStr">
         <is>
-          <t>如果你碰到了它头上的触角，它就会分泌出难闻的气味来保护自己。</t>
+          <t>如果你碰到了它頭上的觸角，它就會分泌出難聞的氣味來保護自己。</t>
         </is>
       </c>
     </row>
@@ -2331,7 +2331,7 @@
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>铁甲蛹</t>
+          <t>鐵甲蛹</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
@@ -2409,7 +2409,7 @@
       </c>
       <c r="S12" s="4" t="inlineStr">
         <is>
-          <t>它会让外壳变硬来保护自己。然而在遇到强烈的冲击力时，它的身体还是会被撞出来。</t>
+          <t>它會讓外殼變硬來保護自己。然而在遇到強烈的衝擊力時，它的身體還是會被撞出來。</t>
         </is>
       </c>
     </row>
@@ -2497,7 +2497,7 @@
       </c>
       <c r="S13" s="4" t="inlineStr">
         <is>
-          <t>它翅膀上的剧毒鳞粉能够防水，因此即使是雨天也可以飞来飞去。</t>
+          <t>它翅膀上的劇毒鱗粉能夠防水，因此即使是雨天也可以飛來飛去。</t>
         </is>
       </c>
     </row>
@@ -2507,7 +2507,7 @@
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>独角虫</t>
+          <t>獨角蟲</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
@@ -2585,7 +2585,7 @@
       </c>
       <c r="S14" s="4" t="inlineStr">
         <is>
-          <t>头上长有尖锐的针。它喜欢藏在森林或草丛里大量吞食树叶。</t>
+          <t>頭上長有尖銳的針。它喜歡藏在森林或草叢裡大量吞食樹葉。</t>
         </is>
       </c>
     </row>
@@ -2595,7 +2595,7 @@
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>铁壳蛹</t>
+          <t>鐵殼蛹</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
@@ -2673,7 +2673,7 @@
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>虽然几乎动也动不了，但是如果遇到了危险，有时似乎会竖起毒刺来反抗。</t>
+          <t>雖然幾乎動也動不了，但是如果遇到了危險，有時似乎會豎起毒刺來反抗。</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>大针蜂</t>
+          <t>大針蜂</t>
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>它会用双手和尾部的３根毒针反复刺伤敌人。</t>
+          <t>它會用雙手和尾部的３根毒針反覆刺傷敵人。</t>
         </is>
       </c>
     </row>
@@ -2849,7 +2849,7 @@
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>性格沉着冷静，即使受到攻击也很少反击，只会朝对手扬起沙子保护自己。</t>
+          <t>性格沉著冷靜，即使受到攻擊也很少反擊，只會朝對手揚起沙子保護自己。</t>
         </is>
       </c>
     </row>
@@ -2859,7 +2859,7 @@
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>比比鸟</t>
+          <t>比比鳥</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">
@@ -2937,7 +2937,7 @@
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>拥有超群的体力，而且飞翔范围广，经常飞到很远的地方寻找食物。</t>
+          <t>擁有超群的體力，而且飛翔範圍廣，經常飛到很遠的地方尋找食物。</t>
         </is>
       </c>
     </row>
@@ -2947,7 +2947,7 @@
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>大比鸟</t>
+          <t>大比鳥</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
@@ -3025,7 +3025,7 @@
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>以２马赫的飞行速度来觅食。它巨大的爪子是非常令人惧怕的武器。</t>
+          <t>以２馬赫的飛行速度來覓食。它巨大的爪子是非常令人懼怕的武器。</t>
         </is>
       </c>
     </row>
@@ -3035,7 +3035,7 @@
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>小拉达</t>
+          <t>小拉達</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
@@ -3113,7 +3113,7 @@
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>有两颗大门牙，见什么咬什么。只要看到１只小拉达出没，附近肯定还住着40只以上。</t>
+          <t>有兩顆大門牙，見什麼咬什麼。只要看到１只小拉達出沒，附近肯定還住著40只以上。</t>
         </is>
       </c>
     </row>
@@ -3123,7 +3123,7 @@
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>拉达</t>
+          <t>拉達</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
@@ -3201,7 +3201,7 @@
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>它的后脚上长着小蹼，以便它在水中游泳寻找食物。</t>
+          <t>它的後腳上長著小蹼，以便它在水中游泳尋找食物。</t>
         </is>
       </c>
     </row>
@@ -3289,7 +3289,7 @@
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>不擅长高空飞行。会以超高速在地盘里四处盘旋，以保护自己的地盘不被侵犯。</t>
+          <t>不擅長高空飛行。會以超高速在地盤裡四處盤旋，以保護自己的地盤不被侵犯。</t>
         </is>
       </c>
     </row>
@@ -3377,7 +3377,7 @@
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>很久以前就存在的宝可梦。哪怕只察觉到一丝危险，都会立即飞向高空。</t>
+          <t>很久以前就存在的寶可夢。哪怕只察覺到一絲危險，都會立即飛向高空。</t>
         </is>
       </c>
     </row>
@@ -3465,7 +3465,7 @@
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>身体会随着年龄增长不断变长。每到夜里，它会一圈圈地将身体缠绕在树枝上休息。</t>
+          <t>身體會隨著年齡增長不斷變長。每到夜裡，它會一圈圈地將身體纏繞在樹枝上休息。</t>
         </is>
       </c>
     </row>
@@ -3553,7 +3553,7 @@
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>根据研究证实，它腹部那可怕的纹路大约有６个种类已经得到确认。</t>
+          <t>根據研究證實，它腹部那可怕的紋路大約有６個種類已經得到確認。</t>
         </is>
       </c>
     </row>
@@ -3641,7 +3641,7 @@
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>会将尾巴竖起来，去感觉周围是否安全。所以，如果随便去拉它的尾巴，会被咬喔。关于皮卡丘的读音，在中国大陆和香港曾多次使用其英文发音，而非普通话或粤语的汉字发音，在台湾则皆使用了国语汉字发音。</t>
+          <t>會將尾巴豎起來，感覺周圍是否安全。如果隨便去拉它的尾巴，會被咬喔。</t>
         </is>
       </c>
     </row>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="S27" s="4" t="inlineStr">
         <is>
-          <t>体内的电力累积到一定程度时，性格会变得带有攻击性。在昏暗处看起来就像是在发亮。</t>
+          <t>體內的電力累積到一定程度時，性格會變得帶有攻擊性。在昏暗處看起來就像是在發亮。</t>
         </is>
       </c>
     </row>
@@ -3817,7 +3817,7 @@
       </c>
       <c r="S28" s="4" t="inlineStr">
         <is>
-          <t>身体很干燥。但据说在夜里降温时，它的表皮上会有露水凝结。</t>
+          <t>身體很乾燥。但據說在夜裡降溫時，它的表皮上會有露水凝結。</t>
         </is>
       </c>
     </row>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="S29" s="4" t="inlineStr">
         <is>
-          <t>它很擅长用爪子抓伤敌人。虽然在战斗中偶尔会折断爪子，但到第二天就会长出新的来。</t>
+          <t>它很擅長用爪子抓傷敵人。雖然在戰鬥中偶爾會折斷爪子，但到第二天就會長出新的來。</t>
         </is>
       </c>
     </row>
@@ -3915,7 +3915,7 @@
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>尼多兰</t>
+          <t>尼多蘭</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="S30" s="4" t="inlineStr">
         <is>
-          <t>虽然它性格温顺不喜欢战斗，但由于小犄角中含有毒液，请一定要小心提防。</t>
+          <t>雖然它性格溫順不喜歡戰鬥，但由於小犄角中含有毒液，請一定要小心提防。</t>
         </is>
       </c>
     </row>
@@ -4081,7 +4081,7 @@
       </c>
       <c r="S31" s="4" t="inlineStr">
         <is>
-          <t>待在巢穴深处的时候，它一定会把身上的刺收起来。这表明它正处于放松状态。</t>
+          <t>待在巢穴深處的時候，它一定會把身上的刺收起來。這表明它正處於放鬆狀態。</t>
         </is>
       </c>
     </row>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="S32" s="4" t="inlineStr">
         <is>
-          <t>坚硬的鳞片覆盖着强壮的身体。据说它的鳞片会自己长出新的。</t>
+          <t>堅硬的鱗片覆蓋著強壯的身體。據說它的鱗片會自己長出新的。</t>
         </is>
       </c>
     </row>
@@ -4257,7 +4257,7 @@
       </c>
       <c r="S33" s="4" t="inlineStr">
         <is>
-          <t>一直竖起它的大耳朵感知周围的情形。当它察觉到危险便会使用毒针。</t>
+          <t>一直豎起它的大耳朵感知周圍的情形。當它察覺到危險便會使用毒針。</t>
         </is>
       </c>
     </row>
@@ -4267,7 +4267,7 @@
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>尼多力诺</t>
+          <t>尼多力諾</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
@@ -4345,7 +4345,7 @@
       </c>
       <c r="S34" s="4" t="inlineStr">
         <is>
-          <t>头上的犄角里含有毒素，当犄角撞穿了什么东西时，毒素就会随着冲击而流出。</t>
+          <t>頭上的犄角裡含有毒素，當犄角撞穿了什麼東西時，毒素就會隨著衝擊而流出。</t>
         </is>
       </c>
     </row>
@@ -4433,7 +4433,7 @@
       </c>
       <c r="S35" s="4" t="inlineStr">
         <is>
-          <t>通过活用自己钢一般坚硬的皮肤来使出强力的撞击。它的犄角坚硬得能够刺穿钻石。</t>
+          <t>會靈活運用鋼鐵般堅硬的皮膚使出強力撞擊。它的犄角堅硬得能夠刺穿鑽石。</t>
         </is>
       </c>
     </row>
@@ -4521,7 +4521,7 @@
       </c>
       <c r="S36" s="4" t="inlineStr">
         <is>
-          <t>因外形和动作可爱而深受大家的喜爱。但或许是由于数量稀少，它们很难被发现。</t>
+          <t>因外形和動作可愛而深受大家的喜愛。但或許是由於數量稀少，它們很難被發現。</t>
         </is>
       </c>
     </row>
@@ -4609,7 +4609,7 @@
       </c>
       <c r="S37" s="4" t="inlineStr">
         <is>
-          <t>妖精的一种。似乎非常珍惜自己的世界，很少在人类面前现身。</t>
+          <t>妖精的一種。似乎非常珍惜自己的世界，很少在人類面前現身。</t>
         </is>
       </c>
     </row>
@@ -4697,7 +4697,7 @@
       </c>
       <c r="S38" s="18" t="inlineStr">
         <is>
-          <t>皮毛和尾巴都非常美丽。随着自身的成长，尾巴的末端会渐渐分开，数量也会增加。</t>
+          <t>皮毛和尾巴都非常美麗。隨著自身的成長，尾巴的末端會漸漸分開，數量也會增加。</t>
         </is>
       </c>
     </row>
@@ -4785,7 +4785,7 @@
       </c>
       <c r="S39" s="4" t="inlineStr">
         <is>
-          <t>传说这种宝可梦是由９位圣者合体之后而诞生的。</t>
+          <t>傳說這種寶可夢是由９位聖者合體之後而誕生的。</t>
         </is>
       </c>
     </row>
@@ -4873,7 +4873,7 @@
       </c>
       <c r="S40" s="4" t="inlineStr">
         <is>
-          <t>它会用圆溜溜的大眼睛盯着对手唱起不可思议的歌曲，这令人舒服的歌曲会让对手睡着。</t>
+          <t>它會用圓溜溜的大眼睛盯著對手唱起不可思議的歌曲，這令人舒服的歌曲會讓對手睡著。</t>
         </is>
       </c>
     </row>
@@ -4961,7 +4961,7 @@
       </c>
       <c r="S41" s="4" t="inlineStr">
         <is>
-          <t>身体非常有弹性，当它用力吸气时，身体可以无限制地膨胀。</t>
+          <t>身體非常有彈性，當它用力吸氣時，身體可以無限制地膨脹。</t>
         </is>
       </c>
     </row>
@@ -5049,7 +5049,7 @@
       </c>
       <c r="S42" s="4" t="inlineStr">
         <is>
-          <t>由于需要调查前方的状况，它会一边从嘴里发出超音波一边飞行。</t>
+          <t>由於需要調查前方的狀況，它會一邊從嘴裡發出超音波一邊飛行。</t>
         </is>
       </c>
     </row>
@@ -5137,7 +5137,7 @@
       </c>
       <c r="S43" s="4" t="inlineStr">
         <is>
-          <t>难以察觉它会从哪里悄悄接近。它会用尖锐的牙咬住对手，同时使劲地吸血。</t>
+          <t>難以察覺它會從哪裡悄悄接近。它會用尖銳的牙咬住對手，同時使勁地吸血。</t>
         </is>
       </c>
     </row>
@@ -5225,7 +5225,7 @@
       </c>
       <c r="S44" s="4" t="inlineStr">
         <is>
-          <t>要是以为它是普通的草而将它拔起，就会听到它的叫声。这让人感到莫名的恐怖。</t>
+          <t>要是以為它是普通的草而將它拔起，就會聽到它的叫聲。這讓人感到莫名的恐怖。</t>
         </is>
       </c>
     </row>
@@ -5313,7 +5313,7 @@
       </c>
       <c r="S45" s="4" t="inlineStr">
         <is>
-          <t>奇臭无比！即使如此，一千个人里总会出现一个人喜欢闻这种味道。</t>
+          <t>奇臭無比！即使如此，一千個人裡總會出現一個人喜歡聞這種味道。</t>
         </is>
       </c>
     </row>
@@ -5401,7 +5401,7 @@
       </c>
       <c r="S46" s="4" t="inlineStr">
         <is>
-          <t>为了散布有毒的花粉而摇动其巨大的花瓣，同时发出震耳的响声。</t>
+          <t>為了散佈有毒的花粉而搖動其巨大的花瓣，同時發出震耳的響聲。</t>
         </is>
       </c>
     </row>
@@ -5489,7 +5489,7 @@
       </c>
       <c r="S47" s="4" t="inlineStr">
         <is>
-          <t>它会通过挖洞来从树根里吸取营养，但大部分营养都会被背上的蘑菇抢走。</t>
+          <t>它會通過挖洞來從樹根裡吸取營養，但大部分營養都會被背上的蘑菇搶走。</t>
         </is>
       </c>
     </row>
@@ -5577,7 +5577,7 @@
       </c>
       <c r="S48" s="4" t="inlineStr">
         <is>
-          <t>由于虫子的精华不断被吸走，在思考的似乎已经不是虫子，而是背上的蘑菇了。</t>
+          <t>由於蟲子的精華不斷被吸走，在思考的似乎已經不是蟲子，而是背上的蘑菇了。</t>
         </is>
       </c>
     </row>
@@ -5665,7 +5665,7 @@
       </c>
       <c r="S49" s="4" t="inlineStr">
         <is>
-          <t>在明亮的地方你便能发现它具有雷达功能的大眼其实是由许多个小眼睛聚集而成的。</t>
+          <t>在明亮的地方你便能發現它具有雷達功能的大眼其實是由許多個小眼睛聚集而成的。</t>
         </is>
       </c>
     </row>
@@ -5675,7 +5675,7 @@
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>摩鲁蛾</t>
+          <t>摩魯蛾</t>
         </is>
       </c>
       <c r="D50" s="6" t="inlineStr">
@@ -5753,7 +5753,7 @@
       </c>
       <c r="S50" s="4" t="inlineStr">
         <is>
-          <t>如果不小心把它翅膀上的鳞粉沾到了身上，那不但会很难去除，更糟的是毒素也会从那里渗入。</t>
+          <t>如果不小心把它翅膀上的鱗粉沾到了身上，那不但會很難去除，更糟的是毒素也會從那裡滲入。</t>
         </is>
       </c>
     </row>
@@ -5841,7 +5841,7 @@
       </c>
       <c r="S51" s="4" t="inlineStr">
         <is>
-          <t>喜欢阴暗的地方。大部分时间都待在地下，只有在洞窟里会经常探头出来。</t>
+          <t>喜歡陰暗的地方。大部分時間都待在地下，只有在洞窟裡會經常探頭出來。</t>
         </is>
       </c>
     </row>
@@ -5929,7 +5929,7 @@
       </c>
       <c r="S52" s="4" t="inlineStr">
         <is>
-          <t>三合一的力量能让它们挖地深至100公里，甚至有报告说它们会引发地震。</t>
+          <t>三合一的力量能讓它們挖地深至100公里，甚至有報告說它們會引發地震。</t>
         </is>
       </c>
     </row>
@@ -6017,7 +6017,7 @@
       </c>
       <c r="S53" s="4" t="inlineStr">
         <is>
-          <t>貌似一到晚上就精力充沛。喜欢又圆又亮的东西，发现了就一定要捡走。</t>
+          <t>貌似一到晚上就精力充沛。喜歡又圓又亮的東西，發現了就一定要撿走。</t>
         </is>
       </c>
     </row>
@@ -6027,7 +6027,7 @@
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
-          <t>猫老大</t>
+          <t>貓老大</t>
         </is>
       </c>
       <c r="D54" s="6" t="inlineStr">
@@ -6105,7 +6105,7 @@
       </c>
       <c r="S54" s="4" t="inlineStr">
         <is>
-          <t>额头上的宝石闪闪发亮！走路的姿态也十分优美，就像女王一样华丽高贵。</t>
+          <t>額頭上的寶石閃閃發亮！走路的姿態也十分優美，就像女王一樣華麗高貴。</t>
         </is>
       </c>
     </row>
@@ -6115,7 +6115,7 @@
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>可达鸭</t>
+          <t>可達鴨</t>
         </is>
       </c>
       <c r="D55" s="6" t="inlineStr">
@@ -6193,7 +6193,7 @@
       </c>
       <c r="S55" s="4" t="inlineStr">
         <is>
-          <t>一直被头痛困扰。能使用念力，但不知道那是否是出于它自己的意识。</t>
+          <t>一直被頭痛困擾。能使用念力，但不知道那是否是出於它自己的意識。</t>
         </is>
       </c>
     </row>
@@ -6203,7 +6203,7 @@
       </c>
       <c r="C56" s="6" t="inlineStr">
         <is>
-          <t>哥达鸭</t>
+          <t>哥達鴨</t>
         </is>
       </c>
       <c r="D56" s="6" t="inlineStr">
@@ -6281,7 +6281,7 @@
       </c>
       <c r="S56" s="4" t="inlineStr">
         <is>
-          <t>它靠修长的四肢和发达的大脚蹼在湖里优雅地游泳。</t>
+          <t>它靠修長的四肢和發達的大腳蹼在湖裡優雅地游泳。</t>
         </is>
       </c>
     </row>
@@ -6369,7 +6369,7 @@
       </c>
       <c r="S57" s="4" t="inlineStr">
         <is>
-          <t>身体轻盈，在树上生活。常因鸡毛蒜皮的小事发火而飞扑到周围的东西上。</t>
+          <t>身體輕盈，在樹上生活。常因雞毛蒜皮的小事發火而飛撲到周圍的東西上。</t>
         </is>
       </c>
     </row>
@@ -6457,7 +6457,7 @@
       </c>
       <c r="S58" s="4" t="inlineStr">
         <is>
-          <t>只有在谁都不在身边的时候才不生气，但几乎没有人目击过这种情况。</t>
+          <t>只有在誰都不在身邊的時候才不生氣，但幾乎沒有人目擊過這種情況。</t>
         </is>
       </c>
     </row>
@@ -6545,7 +6545,7 @@
       </c>
       <c r="S59" s="4" t="inlineStr">
         <is>
-          <t>性格很容易和人亲近，但是会对进入自己领地的敌人狂吠。</t>
+          <t>性格很容易和人親近，但是會對進入自己領地的敵人狂吠。</t>
         </is>
       </c>
     </row>
@@ -6555,7 +6555,7 @@
       </c>
       <c r="C60" s="6" t="inlineStr">
         <is>
-          <t>风速狗</t>
+          <t>風速狗</t>
         </is>
       </c>
       <c r="D60" s="6" t="inlineStr">
@@ -6633,7 +6633,7 @@
       </c>
       <c r="S60" s="4" t="inlineStr">
         <is>
-          <t>中国古老传说中的宝可梦。曾有不计其数的人为它轻巧跑动的身姿而倾倒。</t>
+          <t>中國古老傳說中的寶可夢。曾有不計其數的人為它輕巧跑動的身姿而傾倒。</t>
         </is>
       </c>
     </row>
@@ -6721,7 +6721,7 @@
       </c>
       <c r="S61" s="4" t="inlineStr">
         <is>
-          <t>漩涡的旋转方向好像会因出生地区而不同。比起走路，它更擅长游泳。</t>
+          <t>漩渦的旋轉方向好像會因出生地區而不同。比起走路，它更擅長游泳。</t>
         </is>
       </c>
     </row>
@@ -6809,7 +6809,7 @@
       </c>
       <c r="S62" s="4" t="inlineStr">
         <is>
-          <t>据说它会在要被对手攻击时用腹部的漩涡让对方睡着，趁机逃跑。</t>
+          <t>據說它會在要被對手攻擊時用腹部的漩渦讓對方睡著，趁機逃跑。</t>
         </is>
       </c>
     </row>
@@ -6897,7 +6897,7 @@
       </c>
       <c r="S63" s="4" t="inlineStr">
         <is>
-          <t>他会用全身的肌肉奋力游泳，连奥林匹克选手都甘拜下风。</t>
+          <t>他會用全身的肌肉奮力游泳，連奧林匹克選手都甘拜下風。</t>
         </is>
       </c>
     </row>
@@ -6907,7 +6907,7 @@
       </c>
       <c r="C64" s="6" t="inlineStr">
         <is>
-          <t>凯西</t>
+          <t>凱西</t>
         </is>
       </c>
       <c r="D64" s="6" t="inlineStr">
@@ -6985,7 +6985,7 @@
       </c>
       <c r="S64" s="4" t="inlineStr">
         <is>
-          <t>它每天要睡１８个小时。遇到危险时，即使在睡梦中也可以用瞬间移动来逃脱。</t>
+          <t>它每天要睡１８個小時。遇到危險時，即使在睡夢中也可以用瞬間移動來逃脫。</t>
         </is>
       </c>
     </row>
@@ -7073,7 +7073,7 @@
       </c>
       <c r="S65" s="4" t="inlineStr">
         <is>
-          <t>当勇基拉在附近时，似乎会发生像是时钟倒转这样的怪事。</t>
+          <t>當勇基拉在附近時，似乎會發生像是時鐘倒轉這樣的怪事。</t>
         </is>
       </c>
     </row>
@@ -7161,7 +7161,7 @@
       </c>
       <c r="S66" s="4" t="inlineStr">
         <is>
-          <t>什么事情都能记住。只要是曾经体验过的事情就绝对不会忘记，头脑非常聪明。</t>
+          <t>什麼事情都能記住。只要是曾經體驗過的事情就絕對不會忘記，頭腦非常聰明。</t>
         </is>
       </c>
     </row>
@@ -7249,7 +7249,7 @@
       </c>
       <c r="S67" s="4" t="inlineStr">
         <is>
-          <t>它体格虽小却力大无比。不但如此，它还精通各种格斗技能，实力十分惊人。</t>
+          <t>它體格雖小卻力大無比。不但如此，它還精通各種格鬥技能，實力十分驚人。</t>
         </is>
       </c>
     </row>
@@ -7337,7 +7337,7 @@
       </c>
       <c r="S68" s="4" t="inlineStr">
         <is>
-          <t>只要解开系在腰上的限制它力量的腰带，豪力就会变得势不可挡。</t>
+          <t>只要解開系在腰上的限制它力量的腰帶，豪力就會變得勢不可擋。</t>
         </is>
       </c>
     </row>
@@ -7425,7 +7425,7 @@
       </c>
       <c r="S69" s="4" t="inlineStr">
         <is>
-          <t>仅靠１只手臂的力量便可推动一座山。４只手一起可以打出极为强力的拳击。</t>
+          <t>僅靠１隻手臂的力量便可推動一座山。４隻手一起可以打出極為強力的拳擊。</t>
         </is>
       </c>
     </row>
@@ -7513,7 +7513,7 @@
       </c>
       <c r="S70" s="4" t="inlineStr">
         <is>
-          <t>喜欢温度高，有一定湿度的地方。它会用身上的藤蔓抓小虫来吃。</t>
+          <t>喜歡溫度高，有一定溼度的地方。它會用身上的藤蔓抓小蟲來吃。</t>
         </is>
       </c>
     </row>
@@ -7601,7 +7601,7 @@
       </c>
       <c r="S71" s="4" t="inlineStr">
         <is>
-          <t>它在肚子饿的时候会吞掉周围会动的东西，分泌溶解液让其致命。</t>
+          <t>它在肚子餓的時候會吞掉周圍會動的東西，分泌溶解液讓其致命。</t>
         </is>
       </c>
     </row>
@@ -7689,7 +7689,7 @@
       </c>
       <c r="S72" s="4" t="inlineStr">
         <is>
-          <t>用花蜜的香味引诱猎物。据说被它吞入嘴里的东西，只要1天就会溶解到连骨头都不剩。</t>
+          <t>用花蜜的香味引誘獵物。據說被它吞入嘴裡的東西，只要1天就會溶解到連骨頭都不剩。</t>
         </is>
       </c>
     </row>
@@ -7699,7 +7699,7 @@
       </c>
       <c r="C73" s="6" t="inlineStr">
         <is>
-          <t>玛瑙水母</t>
+          <t>瑪瑙水母</t>
         </is>
       </c>
       <c r="D73" s="6" t="inlineStr">
@@ -7777,7 +7777,7 @@
       </c>
       <c r="S73" s="4" t="inlineStr">
         <is>
-          <t>有时能在沙滩上发现它干巴巴的身体，但是它只要沾到水就能复活。</t>
+          <t>有時能在沙灘上發現它乾巴巴的身體，但是它只要沾到水就能復活。</t>
         </is>
       </c>
     </row>
@@ -7865,7 +7865,7 @@
       </c>
       <c r="S74" s="4" t="inlineStr">
         <is>
-          <t>它能让80条触手自由伸缩，靠缠住猎物后注入毒素来让其变弱。</t>
+          <t>它能讓80條觸手自由伸縮，靠纏住獵物後注入毒素來讓其變弱。</t>
         </is>
       </c>
     </row>
@@ -7953,7 +7953,7 @@
       </c>
       <c r="S75" s="4" t="inlineStr">
         <is>
-          <t>大多栖息于山路。由于不留神踩到它会使它大发雷霆，得多加小心。</t>
+          <t>大多棲息于山路。由於不留神踩到它會使它大發雷霆，得多加小心。</t>
         </is>
       </c>
     </row>
@@ -8041,7 +8041,7 @@
       </c>
       <c r="S76" s="4" t="inlineStr">
         <is>
-          <t>常在山路上滚来滚去。滚动时从来不关心前面的路上都有什么。</t>
+          <t>常在山路上滾來滾去。滾動時從來不關心前面的路上都有什麼。</t>
         </is>
       </c>
     </row>
@@ -8051,7 +8051,7 @@
       </c>
       <c r="C77" s="6" t="inlineStr">
         <is>
-          <t>隆隆岩</t>
+          <t>隆隆巖</t>
         </is>
       </c>
       <c r="D77" s="6" t="inlineStr">
@@ -8129,7 +8129,7 @@
       </c>
       <c r="S77" s="4" t="inlineStr">
         <is>
-          <t>刚蜕皮时浑身都白白的非常柔软，但是接触到空气之后会迅速变坚硬。</t>
+          <t>剛蛻皮時渾身都白白的非常柔軟，但是接觸到空氣之後會迅速變堅硬。</t>
         </is>
       </c>
     </row>
@@ -8139,7 +8139,7 @@
       </c>
       <c r="C78" s="6" t="inlineStr">
         <is>
-          <t>小火马</t>
+          <t>小火馬</t>
         </is>
       </c>
       <c r="D78" s="6" t="inlineStr">
@@ -8217,7 +8217,7 @@
       </c>
       <c r="S78" s="4" t="inlineStr">
         <is>
-          <t>在用力跳跃之后，会用蹄子和脚上的肌肉来缓解着地时的撞击。</t>
+          <t>在用力跳躍之後，會用蹄子和腳上的肌肉來緩解著地時的撞擊。</t>
         </is>
       </c>
     </row>
@@ -8227,7 +8227,7 @@
       </c>
       <c r="C79" s="6" t="inlineStr">
         <is>
-          <t>烈焰马</t>
+          <t>烈焰馬</t>
         </is>
       </c>
       <c r="D79" s="6" t="inlineStr">
@@ -8305,7 +8305,7 @@
       </c>
       <c r="S79" s="4" t="inlineStr">
         <is>
-          <t>总之就是喜欢跑步。如果发现有谁跑得比自己更快，就会用尽全力去追赶。</t>
+          <t>總之就是喜歡跑步。如果發現有誰跑得比自己更快，就會用盡全力去追趕。</t>
         </is>
       </c>
     </row>
@@ -8315,7 +8315,7 @@
       </c>
       <c r="C80" s="6" t="inlineStr">
         <is>
-          <t>呆呆兽</t>
+          <t>呆呆獸</t>
         </is>
       </c>
       <c r="D80" s="6" t="inlineStr">
@@ -8393,7 +8393,7 @@
       </c>
       <c r="S80" s="4" t="inlineStr">
         <is>
-          <t>非常呆，动作也很缓慢。从不在意时间的流逝，过着悠闲的生活。</t>
+          <t>非常呆，動作也很緩慢。從不在意時間的流逝，過著悠閒的生活。</t>
         </is>
       </c>
     </row>
@@ -8403,7 +8403,7 @@
       </c>
       <c r="C81" s="6" t="inlineStr">
         <is>
-          <t>呆壳兽</t>
+          <t>呆殼獸</t>
         </is>
       </c>
       <c r="D81" s="6" t="inlineStr">
@@ -8481,7 +8481,7 @@
       </c>
       <c r="S81" s="4" t="inlineStr">
         <is>
-          <t>在海边悠闲地生活。如果尾巴上的大舌贝脱落了，它就会变回呆呆兽。</t>
+          <t>在海邊悠閒地生活。如果尾巴上的大舌貝脫落了，它就會變回呆呆獸。</t>
         </is>
       </c>
     </row>
@@ -8569,7 +8569,7 @@
       </c>
       <c r="S82" s="4" t="inlineStr">
         <is>
-          <t>天生就拥有遮断重力的能力，可以一边发出电磁波一边在空中移动。</t>
+          <t>天生就擁有遮斷重力的能力，可以一邊發出電磁波一邊在空中移動。</t>
         </is>
       </c>
     </row>
@@ -8657,7 +8657,7 @@
       </c>
       <c r="S83" s="4" t="inlineStr">
         <is>
-          <t>一直在发射神秘的电波，半径１公里内的气温会升高２度。</t>
+          <t>一直在發射神秘的電波，半徑１公里內的氣溫會升高２度。</t>
         </is>
       </c>
     </row>
@@ -8667,7 +8667,7 @@
       </c>
       <c r="C84" s="6" t="inlineStr">
         <is>
-          <t>大葱鸭</t>
+          <t>大蔥鴨</t>
         </is>
       </c>
       <c r="D84" s="6" t="inlineStr">
@@ -8745,7 +8745,7 @@
       </c>
       <c r="S84" s="4" t="inlineStr">
         <is>
-          <t>居住在茎状植物生长的地方。由于这种植物极为稀少而罕见，大葱鸭的数量似乎也在减少。</t>
+          <t>居住在莖狀植物生長的地方。由於這種植物極為稀少而罕見，大蔥鴨的數量似乎也在減少。</t>
         </is>
       </c>
     </row>
@@ -8833,7 +8833,7 @@
       </c>
       <c r="S85" s="4" t="inlineStr">
         <is>
-          <t>羽毛较短所以不擅长飞行，但是拥有发达的双脚，能够以很快的速度奔跑。</t>
+          <t>羽毛較短所以不擅長飛行，但是擁有發達的雙腳，能夠以很快的速度奔跑。</t>
         </is>
       </c>
     </row>
@@ -8921,7 +8921,7 @@
       </c>
       <c r="S86" s="4" t="inlineStr">
         <is>
-          <t>由嘟嘟的某个头分裂出的变种。以60千米的时速在草原上奔跑。</t>
+          <t>由嘟嘟的某個頭分裂出的變種。以60千米的時速在草原上奔跑。</t>
         </is>
       </c>
     </row>
@@ -8931,7 +8931,7 @@
       </c>
       <c r="C87" s="6" t="inlineStr">
         <is>
-          <t>小海狮</t>
+          <t>小海獅</t>
         </is>
       </c>
       <c r="D87" s="6" t="inlineStr">
@@ -9009,7 +9009,7 @@
       </c>
       <c r="S87" s="4" t="inlineStr">
         <is>
-          <t>喜欢天寒地冻的地方，就算零下10度也能愉快地游泳。</t>
+          <t>喜歡天寒地凍的地方，就算零下10度也能愉快地游泳。</t>
         </is>
       </c>
     </row>
@@ -9019,7 +9019,7 @@
       </c>
       <c r="C88" s="6" t="inlineStr">
         <is>
-          <t>白海狮</t>
+          <t>白海獅</t>
         </is>
       </c>
       <c r="D88" s="6" t="inlineStr">
@@ -9097,7 +9097,7 @@
       </c>
       <c r="S88" s="4" t="inlineStr">
         <is>
-          <t>全身像雪一样白。十分耐寒，即使是在有浮冰的大海里也能很精神地游来游去。</t>
+          <t>全身像雪一樣白。十分耐寒，即使是在有浮冰的大海裡也能很精神地游來游去。</t>
         </is>
       </c>
     </row>
@@ -9185,7 +9185,7 @@
       </c>
       <c r="S89" s="4" t="inlineStr">
         <is>
-          <t>它由囤积的淤泥而形成。臭到让人无法碰触，凡是它走过的地方都寸草不生。</t>
+          <t>它由囤積的淤泥而形成。臭到讓人無法碰觸，凡是它走過的地方都寸草不生。</t>
         </is>
       </c>
     </row>
@@ -9273,7 +9273,7 @@
       </c>
       <c r="S90" s="4" t="inlineStr">
         <is>
-          <t>非常难闻！气味臭到让人窒息，但由于鼻子的退化，它自己完全闻不到味道。</t>
+          <t>非常難聞！氣味臭到讓人窒息，但由於鼻子的退化，它自己完全聞不到味道。</t>
         </is>
       </c>
     </row>
@@ -9283,7 +9283,7 @@
       </c>
       <c r="C91" s="6" t="inlineStr">
         <is>
-          <t>大舌贝</t>
+          <t>大舌貝</t>
         </is>
       </c>
       <c r="D91" s="6" t="inlineStr">
@@ -9361,7 +9361,7 @@
       </c>
       <c r="S91" s="4" t="inlineStr">
         <is>
-          <t>它的硬壳可以承受任何攻击，但是一旦硬壳打开，它柔软的内部就会完全暴露。</t>
+          <t>它的硬殼可以承受任何攻擊，但是一旦硬殼打開，它柔軟的內部就會完全暴露。</t>
         </is>
       </c>
     </row>
@@ -9371,7 +9371,7 @@
       </c>
       <c r="C92" s="6" t="inlineStr">
         <is>
-          <t>刺甲贝</t>
+          <t>刺甲貝</t>
         </is>
       </c>
       <c r="D92" s="6" t="inlineStr">
@@ -9449,7 +9449,7 @@
       </c>
       <c r="S92" s="4" t="inlineStr">
         <is>
-          <t>不但有比钻石还要坚硬的外壳保护着，还能发射壳上的刺，不太好对付。</t>
+          <t>不但有比鑽石還要堅硬的外殼保護著，還能發射殼上的刺，不太好對付。</t>
         </is>
       </c>
     </row>
@@ -9539,7 +9539,7 @@
       </c>
       <c r="S93" s="4" t="inlineStr">
         <is>
-          <t>它似乎会在没人居住的旧屋子里出现。形状不清，仿佛就像是气体一样。</t>
+          <t>它似乎會在沒人居住的舊屋子裡出現。形狀不清，彷彿就像是氣體一樣。</t>
         </is>
       </c>
     </row>
@@ -9627,7 +9627,7 @@
       </c>
       <c r="S94" s="4" t="inlineStr">
         <is>
-          <t>被它舔到时生命力会被吸走，身体会不受控制地不停颤抖，最后一命呜呼。</t>
+          <t>被它舔到時生命力會被吸走，身體會不受控制地不停顫抖，最後一命嗚呼。</t>
         </is>
       </c>
     </row>
@@ -9715,7 +9715,7 @@
       </c>
       <c r="S95" s="4" t="inlineStr">
         <is>
-          <t>如果你突然感到寒气逼近，就说明耿鬼在你身边，或许它已经在你身上下了诅咒。</t>
+          <t>如果你突然感到寒氣逼近，就說明耿鬼在你身邊，或許它已經在你身上下了詛咒。</t>
         </is>
       </c>
     </row>
@@ -9725,7 +9725,7 @@
       </c>
       <c r="C96" s="6" t="inlineStr">
         <is>
-          <t>大岩蛇</t>
+          <t>大巖蛇</t>
         </is>
       </c>
       <c r="D96" s="6" t="inlineStr">
@@ -9803,7 +9803,7 @@
       </c>
       <c r="S96" s="4" t="inlineStr">
         <is>
-          <t>以惊人之势钻地觅食。在它通过之后形成的洞穴会被地鼠们当作自己的住处。</t>
+          <t>以驚人之勢鑽地覓食。在它經過之後形成的洞穴會被地鼠們當作自己的住處。</t>
         </is>
       </c>
     </row>
@@ -9891,7 +9891,7 @@
       </c>
       <c r="S97" s="4" t="inlineStr">
         <is>
-          <t>如果你每晚与它一起睡觉，它偶尔会让你梦见它以前吃过的梦。</t>
+          <t>如果你每晚與它一起睡覺，它偶爾會讓你夢見它以前吃過的夢。</t>
         </is>
       </c>
     </row>
@@ -9901,7 +9901,7 @@
       </c>
       <c r="C98" s="6" t="inlineStr">
         <is>
-          <t>引梦貘人</t>
+          <t>引夢貘人</t>
         </is>
       </c>
       <c r="D98" s="6" t="inlineStr">
@@ -9979,7 +9979,7 @@
       </c>
       <c r="S98" s="4" t="inlineStr">
         <is>
-          <t>无意中遇到它的时候，如果不小心和它对上视线会很危险。它手里拿着的钟摆会让人睡着。</t>
+          <t>無意中遇到它的時候，如果不小心和它對上視線會很危險。它手裡拿著的鐘擺會讓人睡著。</t>
         </is>
       </c>
     </row>
@@ -9989,7 +9989,7 @@
       </c>
       <c r="C99" s="6" t="inlineStr">
         <is>
-          <t>大钳蟹</t>
+          <t>大鉗蟹</t>
         </is>
       </c>
       <c r="D99" s="6" t="inlineStr">
@@ -10067,7 +10067,7 @@
       </c>
       <c r="S99" s="4" t="inlineStr">
         <is>
-          <t>钳子是它强悍的武器，但在攻击时钳子偶尔会脱落。脱落后很快会长出新的来。</t>
+          <t>鉗子是它強悍的武器，但在攻擊時鉗子偶爾會脫落。脫落後很快會長出新的來。</t>
         </is>
       </c>
     </row>
@@ -10077,7 +10077,7 @@
       </c>
       <c r="C100" s="6" t="inlineStr">
         <is>
-          <t>巨钳蟹</t>
+          <t>巨鉗蟹</t>
         </is>
       </c>
       <c r="D100" s="6" t="inlineStr">
@@ -10155,7 +10155,7 @@
       </c>
       <c r="S100" s="4" t="inlineStr">
         <is>
-          <t>一边的钳子很是巨大，虽说硬如钢铁还拥有１万马力，但还是太重了。</t>
+          <t>一邊的鉗子很是巨大，雖說硬如鋼鐵還擁有１萬馬力，但還是太重了。</t>
         </is>
       </c>
     </row>
@@ -10165,7 +10165,7 @@
       </c>
       <c r="C101" s="6" t="inlineStr">
         <is>
-          <t>霹雳电球</t>
+          <t>霹靂電球</t>
         </is>
       </c>
       <c r="D101" s="6" t="inlineStr">
@@ -10243,7 +10243,7 @@
       </c>
       <c r="S101" s="4" t="inlineStr">
         <is>
-          <t>据说它与精灵球相似的外形其实是它的保护色，但它很容易自爆这一点也出人意料。</t>
+          <t>據說它與精靈球相似的外形其實是它的保護色，但它很容易自爆這一點也出人意料。</t>
         </is>
       </c>
     </row>
@@ -10253,7 +10253,7 @@
       </c>
       <c r="C102" s="6" t="inlineStr">
         <is>
-          <t>顽皮雷弹</t>
+          <t>頑皮雷彈</t>
         </is>
       </c>
       <c r="D102" s="6" t="inlineStr">
@@ -10331,7 +10331,7 @@
       </c>
       <c r="S102" s="4" t="inlineStr">
         <is>
-          <t>只要受到一点撞击，就会由于体内的电能溢出导致爆炸。</t>
+          <t>只要受到一點撞擊，就會由於體內的電能溢出導致爆炸。</t>
         </is>
       </c>
     </row>
@@ -10419,7 +10419,7 @@
       </c>
       <c r="S103" s="4" t="inlineStr">
         <is>
-          <t>每一个蛋都相互吸引着旋转。６个蛋凑不齐时它就无法保持平衡。</t>
+          <t>每一個蛋都相互吸引著旋轉。６個蛋湊不齊時它就無法保持平衡。</t>
         </is>
       </c>
     </row>
@@ -10429,7 +10429,7 @@
       </c>
       <c r="C104" s="6" t="inlineStr">
         <is>
-          <t>椰蛋树</t>
+          <t>椰蛋樹</t>
         </is>
       </c>
       <c r="D104" s="6" t="inlineStr">
@@ -10507,7 +10507,7 @@
       </c>
       <c r="S104" s="4" t="inlineStr">
         <is>
-          <t>由于三个头各自都在思考自己喜欢的事情，所以它的叫声非常吵闹。</t>
+          <t>由於三個頭各自都在思考自己喜歡的事情，所以它的叫聲非常吵鬧。</t>
         </is>
       </c>
     </row>
@@ -10595,7 +10595,7 @@
       </c>
       <c r="S105" s="4" t="inlineStr">
         <is>
-          <t>它头上戴着死去母亲的头骨。它的哭声会在头骨里回响出悲伤的旋律。</t>
+          <t>它頭上戴著死去母親的頭骨。它的哭聲會在頭骨裡迴響出悲傷的旋律。</t>
         </is>
       </c>
     </row>
@@ -10683,7 +10683,7 @@
       </c>
       <c r="S106" s="4" t="inlineStr">
         <is>
-          <t>身体曾经又小又弱，在习惯了使用骨头战斗后才变成了粗暴的性格。</t>
+          <t>身體曾經又小又弱，在習慣了使用骨頭戰鬥後才變成了粗暴的性格。</t>
         </is>
       </c>
     </row>
@@ -10693,7 +10693,7 @@
       </c>
       <c r="C107" s="6" t="inlineStr">
         <is>
-          <t>飞腿郎</t>
+          <t>飛腿郎</t>
         </is>
       </c>
       <c r="D107" s="6" t="inlineStr">
@@ -10771,7 +10771,7 @@
       </c>
       <c r="S107" s="4" t="inlineStr">
         <is>
-          <t>在踢中敌人的瞬间，脚底会变得像钻石般坚硬，将对手踢成碎片。</t>
+          <t>在踢中敵人的瞬間，腳底會變得像鑽石般堅硬，將對手踢成碎片。</t>
         </is>
       </c>
     </row>
@@ -10859,7 +10859,7 @@
       </c>
       <c r="S108" s="4" t="inlineStr">
         <is>
-          <t>它的拳击好似钻头一般！在它的攻击之下，哪怕是水泥墙也会被钻出洞来。</t>
+          <t>它的拳擊好似鑽頭一般！在它的攻擊之下，哪怕是水泥牆也會被鑽出洞來。</t>
         </is>
       </c>
     </row>
@@ -10869,7 +10869,7 @@
       </c>
       <c r="C109" s="6" t="inlineStr">
         <is>
-          <t>大舌头</t>
+          <t>大舌頭</t>
         </is>
       </c>
       <c r="D109" s="6" t="inlineStr">
@@ -10947,7 +10947,7 @@
       </c>
       <c r="S109" s="4" t="inlineStr">
         <is>
-          <t>它２米长的舌头比前肢更能灵活地移动。不知为何，被它舔到之后会觉得发麻。</t>
+          <t>它２米長的舌頭比前肢更能靈活地移動。不知為何，被它舔到之後會覺得發麻。</t>
         </is>
       </c>
     </row>
@@ -10957,7 +10957,7 @@
       </c>
       <c r="C110" s="6" t="inlineStr">
         <is>
-          <t>瓦斯弹</t>
+          <t>瓦斯彈</t>
         </is>
       </c>
       <c r="D110" s="6" t="inlineStr">
@@ -11035,7 +11035,7 @@
       </c>
       <c r="S110" s="4" t="inlineStr">
         <is>
-          <t>在炎热的地方，它体内的气体会由于膨胀而产生爆炸的危险，需要注意。</t>
+          <t>在炎熱的地方，它體內的氣體會由於膨脹而產生爆炸的危險，需要注意。</t>
         </is>
       </c>
     </row>
@@ -11045,7 +11045,7 @@
       </c>
       <c r="C111" s="6" t="inlineStr">
         <is>
-          <t>双弹瓦斯</t>
+          <t>雙彈瓦斯</t>
         </is>
       </c>
       <c r="D111" s="6" t="inlineStr">
@@ -11123,7 +11123,7 @@
       </c>
       <c r="S111" s="4" t="inlineStr">
         <is>
-          <t>它要靠吸收垃圾里的毒气、细菌和灰尘来维持生命。</t>
+          <t>它要靠吸收垃圾裡的毒氣、細菌和灰塵來維持生命。</t>
         </is>
       </c>
     </row>
@@ -11133,7 +11133,7 @@
       </c>
       <c r="C112" s="6" t="inlineStr">
         <is>
-          <t>独角犀牛</t>
+          <t>獨角犀牛</t>
         </is>
       </c>
       <c r="D112" s="6" t="inlineStr">
@@ -11211,7 +11211,7 @@
       </c>
       <c r="S112" s="4" t="inlineStr">
         <is>
-          <t>单细胞的脑子只能思考一件事情。一旦它开始猛撞，直到睡着前都不会停止。</t>
+          <t>單細胞的腦子只能思考一件事情。一旦它開始猛撞，直到睡著前都不會停止。</t>
         </is>
       </c>
     </row>
@@ -11221,7 +11221,7 @@
       </c>
       <c r="C113" s="6" t="inlineStr">
         <is>
-          <t>钻角犀兽</t>
+          <t>鑽角犀獸</t>
         </is>
       </c>
       <c r="D113" s="6" t="inlineStr">
@@ -11299,7 +11299,7 @@
       </c>
       <c r="S113" s="4" t="inlineStr">
         <is>
-          <t>可以只用后腿行走，智力也发达了许多。像盔甲一样的皮肤可以抵挡住岩浆。</t>
+          <t>可以只用後腿行走，智力也發達了許多。像盔甲一樣的皮膚可以抵擋住岩漿。</t>
         </is>
       </c>
     </row>
@@ -11387,7 +11387,7 @@
       </c>
       <c r="S114" s="4" t="inlineStr">
         <is>
-          <t>性格温柔的宝可梦，当它看到受伤的宝可梦时，会把营养丰富的蛋分给对方。</t>
+          <t>性格溫柔的寶可夢，當它看到受傷的寶可夢時，會把營養豐富的蛋分給對方。</t>
         </is>
       </c>
     </row>
@@ -11475,7 +11475,7 @@
       </c>
       <c r="S115" s="4" t="inlineStr">
         <is>
-          <t>全身被蓝色的蔓藤覆盖，真面目不为人知。据说，它的蔓藤会持续不断地生长。</t>
+          <t>全身被藍色的蔓藤覆蓋，真面目不為人知。據說，它的蔓藤會持續不斷地生長。</t>
         </is>
       </c>
     </row>
@@ -11485,7 +11485,7 @@
       </c>
       <c r="C116" s="6" t="inlineStr">
         <is>
-          <t>袋兽</t>
+          <t>袋獸</t>
         </is>
       </c>
       <c r="D116" s="6" t="inlineStr">
@@ -11563,7 +11563,7 @@
       </c>
       <c r="S116" s="4" t="inlineStr">
         <is>
-          <t>在腹部的袋子里养育自己的宝宝。为了保护宝宝，遇到什么样的敌人都不会退缩。</t>
+          <t>在腹部的袋子裡養育自己的寶寶。為了保護寶寶，遇到什麼樣的敵人都不會退縮。</t>
         </is>
       </c>
     </row>
@@ -11573,7 +11573,7 @@
       </c>
       <c r="C117" s="6" t="inlineStr">
         <is>
-          <t>墨海马</t>
+          <t>墨海馬</t>
         </is>
       </c>
       <c r="D117" s="6" t="inlineStr">
@@ -11651,7 +11651,7 @@
       </c>
       <c r="S117" s="4" t="inlineStr">
         <is>
-          <t>在感到危险时会从嘴里用力地喷出水或者特殊的墨汁。</t>
+          <t>在感到危險時會從嘴裡用力地噴出水或者特殊的墨汁。</t>
         </is>
       </c>
     </row>
@@ -11661,7 +11661,7 @@
       </c>
       <c r="C118" s="6" t="inlineStr">
         <is>
-          <t>海刺龙</t>
+          <t>海刺龍</t>
         </is>
       </c>
       <c r="D118" s="6" t="inlineStr">
@@ -11739,7 +11739,7 @@
       </c>
       <c r="S118" s="4" t="inlineStr">
         <is>
-          <t>摸它的背鳍会导致麻痹。为了避免在睡觉时被水冲走，它会用尾巴缠住珊瑚。</t>
+          <t>摸它的背鰭會導致麻痺。為了避免在睡覺時被水沖走，它會用尾巴纏住珊瑚。</t>
         </is>
       </c>
     </row>
@@ -11749,7 +11749,7 @@
       </c>
       <c r="C119" s="6" t="inlineStr">
         <is>
-          <t>角金鱼</t>
+          <t>角金魚</t>
         </is>
       </c>
       <c r="D119" s="6" t="inlineStr">
@@ -11827,7 +11827,7 @@
       </c>
       <c r="S119" s="4" t="inlineStr">
         <is>
-          <t>到了产卵期你就可以看到成群的角金鱼逆流而行或是攀登瀑布。</t>
+          <t>到了產卵期你就可以看到成群的角金魚逆流而行或是攀登瀑布。</t>
         </is>
       </c>
     </row>
@@ -11837,7 +11837,7 @@
       </c>
       <c r="C120" s="6" t="inlineStr">
         <is>
-          <t>金鱼王</t>
+          <t>金魚王</t>
         </is>
       </c>
       <c r="D120" s="6" t="inlineStr">
@@ -11915,7 +11915,7 @@
       </c>
       <c r="S120" s="4" t="inlineStr">
         <is>
-          <t>雄性的职责是用头上的角打穿河里的石头筑巢。</t>
+          <t>雄性的職責是用頭上的角打穿河裡的石頭築巢。</t>
         </is>
       </c>
     </row>
@@ -12003,7 +12003,7 @@
       </c>
       <c r="S121" s="4" t="inlineStr">
         <is>
-          <t>据说只要它身体的中心部分还存活着，即使被切成小块也能再生。</t>
+          <t>據說只要它身體的中心部分還存活著，即使被切成小塊也能再生。</t>
         </is>
       </c>
     </row>
@@ -12013,7 +12013,7 @@
       </c>
       <c r="C122" s="6" t="inlineStr">
         <is>
-          <t>宝石海星</t>
+          <t>寶石海星</t>
         </is>
       </c>
       <c r="D122" s="6" t="inlineStr">
@@ -12091,7 +12091,7 @@
       </c>
       <c r="S122" s="4" t="inlineStr">
         <is>
-          <t>据说当被称为其核心的中心部分闪烁着七色光芒时，就代表着它正在传达信息。</t>
+          <t>據說當被稱為其核心的中心部分閃爍著七色光芒時，就代表著它正在傳達訊息。</t>
         </is>
       </c>
     </row>
@@ -12101,7 +12101,7 @@
       </c>
       <c r="C123" s="6" t="inlineStr">
         <is>
-          <t>魔墙人偶</t>
+          <t>魔牆人偶</t>
         </is>
       </c>
       <c r="D123" s="6" t="inlineStr">
@@ -12179,7 +12179,7 @@
       </c>
       <c r="S123" s="4" t="inlineStr">
         <is>
-          <t>擅长表演哑剧，一直都在练习。即使空无一物，也能让人觉得那里真的有东西存在。</t>
+          <t>擅長表演啞劇，一直都在練習。即使空無一物，也能讓人覺得那裡真的有東西存在。</t>
         </is>
       </c>
     </row>
@@ -12189,7 +12189,7 @@
       </c>
       <c r="C124" s="6" t="inlineStr">
         <is>
-          <t>飞天螳螂</t>
+          <t>飛天螳螂</t>
         </is>
       </c>
       <c r="D124" s="6" t="inlineStr">
@@ -12267,7 +12267,7 @@
       </c>
       <c r="S124" s="4" t="inlineStr">
         <is>
-          <t>突然从草丛里窜出来，用锋利的镰刀斩砍的样子仿佛就像是忍者。</t>
+          <t>突然從草叢裡竄出來，用鋒利的鐮刀斬砍的樣子彷彿就像是忍者。</t>
         </is>
       </c>
     </row>
@@ -12355,7 +12355,7 @@
       </c>
       <c r="S125" s="4" t="inlineStr">
         <is>
-          <t>以独特的节奏悠然移动，仿佛是在跳舞。走路的姿势如同在扭腰一样。</t>
+          <t>以獨特的節奏悠然移動，彷彿是在跳舞。走路的姿勢如同在扭腰一樣。</t>
         </is>
       </c>
     </row>
@@ -12365,7 +12365,7 @@
       </c>
       <c r="C126" s="6" t="inlineStr">
         <is>
-          <t>电击兽</t>
+          <t>電擊獸</t>
         </is>
       </c>
       <c r="D126" s="6" t="inlineStr">
@@ -12443,7 +12443,7 @@
       </c>
       <c r="S126" s="4" t="inlineStr">
         <is>
-          <t>要是发生了大片的停电，那一定是电击兽偷偷吃掉了发电站的电能。</t>
+          <t>要是發生了大片的停電，那一定是電擊獸偷偷吃掉了發電站的電能。</t>
         </is>
       </c>
     </row>
@@ -12453,7 +12453,7 @@
       </c>
       <c r="C127" s="6" t="inlineStr">
         <is>
-          <t>鸭嘴火兽</t>
+          <t>鴨嘴火獸</t>
         </is>
       </c>
       <c r="D127" s="6" t="inlineStr">
@@ -12531,7 +12531,7 @@
       </c>
       <c r="S127" s="4" t="inlineStr">
         <is>
-          <t>出生在火山口。因为它的全身都在燃烧，所以人们难以分辨它和火球的区别。</t>
+          <t>出生在火山口。因為它的全身都在燃燒，所以人們難以分辨它和火球的區別。</t>
         </is>
       </c>
     </row>
@@ -12541,7 +12541,7 @@
       </c>
       <c r="C128" s="6" t="inlineStr">
         <is>
-          <t>凯罗斯</t>
+          <t>凱羅斯</t>
         </is>
       </c>
       <c r="D128" s="6" t="inlineStr">
@@ -12619,7 +12619,7 @@
       </c>
       <c r="S128" s="4" t="inlineStr">
         <is>
-          <t>用犄角全力夹击！由于低温会使它无法动弹，所以它会选择在温暖的地方生活。</t>
+          <t>用犄角全力夾擊！由於低溫會使它無法動彈，所以它會選擇在溫暖的地方生活。</t>
         </is>
       </c>
     </row>
@@ -12629,7 +12629,7 @@
       </c>
       <c r="C129" s="6" t="inlineStr">
         <is>
-          <t>肯泰罗</t>
+          <t>肯泰羅</t>
         </is>
       </c>
       <c r="D129" s="6" t="inlineStr">
@@ -12707,7 +12707,7 @@
       </c>
       <c r="S129" s="4" t="inlineStr">
         <is>
-          <t>精力充沛且个性火暴。一旦开始奔跑，在撞到东西之前都不会停下脚步。</t>
+          <t>精力充沛且個性火暴。一旦開始奔跑，在撞到東西之前都不會停下腳步。</t>
         </is>
       </c>
     </row>
@@ -12717,7 +12717,7 @@
       </c>
       <c r="C130" s="6" t="inlineStr">
         <is>
-          <t>鲤鱼王</t>
+          <t>鯉魚王</t>
         </is>
       </c>
       <c r="D130" s="6" t="inlineStr">
@@ -12795,7 +12795,7 @@
       </c>
       <c r="S130" s="4" t="inlineStr">
         <is>
-          <t>因靠不住而出名的宝可梦。海里、河里、池子里、还有水洼里……它们会在各种地方游来游去。</t>
+          <t>因靠不住而出名的寶可夢。海裡、河裡、池子裡、還有水窪裡……它們會在各種地方游來游去。</t>
         </is>
       </c>
     </row>
@@ -12805,7 +12805,7 @@
       </c>
       <c r="C131" s="6" t="inlineStr">
         <is>
-          <t>暴鲤龙</t>
+          <t>暴鯉龍</t>
         </is>
       </c>
       <c r="D131" s="6" t="inlineStr">
@@ -12883,7 +12883,7 @@
       </c>
       <c r="S131" s="4" t="inlineStr">
         <is>
-          <t>性格蛮横喜欢破坏。在古代，这个恐怖的宝可梦曾经有过把整座城市烧成焦土的记录。</t>
+          <t>性格蠻橫喜歡破壞。在古代，這個恐怖的寶可夢曾經有過把整座城市燒成焦土的記錄。</t>
         </is>
       </c>
     </row>
@@ -12971,7 +12971,7 @@
       </c>
       <c r="S132" s="4" t="inlineStr">
         <is>
-          <t>它拥有可以理解人类语言的温柔之心。会把人载在背上渡过大海。</t>
+          <t>它擁有可以理解人類語言的溫柔之心。會把人載在背上渡過大海。</t>
         </is>
       </c>
     </row>
@@ -12981,7 +12981,7 @@
       </c>
       <c r="C133" s="6" t="inlineStr">
         <is>
-          <t>百变怪</t>
+          <t>百變怪</t>
         </is>
       </c>
       <c r="D133" s="6" t="inlineStr">
@@ -13059,7 +13059,7 @@
       </c>
       <c r="S133" s="4" t="inlineStr">
         <is>
-          <t>看到敌人的一瞬间身体便如同要融化一般开始转变，几乎能变身成和对方完全相同的样子。</t>
+          <t>看到敵人的一瞬間身體便如同要融化一般開始轉變，幾乎能變身成和對方完全相同的樣子。</t>
         </is>
       </c>
     </row>
@@ -13147,7 +13147,7 @@
       </c>
       <c r="S134" s="4" t="inlineStr">
         <is>
-          <t>由于基因不稳定，进化的可能多种多样。只是生存数量很少。</t>
+          <t>由於基因不穩定，進化的可能多種多樣。只是生存數量很少。</t>
         </is>
       </c>
     </row>
@@ -13235,7 +13235,7 @@
       </c>
       <c r="S135" s="4" t="inlineStr">
         <is>
-          <t>它的细胞与水分子相似，在它溶入于水后，你就完全看不见它了。</t>
+          <t>它的細胞與水分子相似，在它溶入於水後，你就完全看不見它了。</t>
         </is>
       </c>
     </row>
@@ -13323,7 +13323,7 @@
       </c>
       <c r="S136" s="4" t="inlineStr">
         <is>
-          <t>稍微受点刺激就会大叫或生气，每当心情变化时都会蓄电。</t>
+          <t>稍微受點刺激就會大叫或生氣，每當心情變化時都會蓄電。</t>
         </is>
       </c>
     </row>
@@ -13411,7 +13411,7 @@
       </c>
       <c r="S137" s="4" t="inlineStr">
         <is>
-          <t>体内的火袋能让它将吸入的气体转化为１７００度的火焰，接着从口中喷出。</t>
+          <t>體內的火袋能讓它將吸入的氣體轉化為１７００度的火焰，接著從口中噴出。</t>
         </is>
       </c>
     </row>
@@ -13421,7 +13421,7 @@
       </c>
       <c r="C138" s="6" t="inlineStr">
         <is>
-          <t>多边兽</t>
+          <t>多邊獸</t>
         </is>
       </c>
       <c r="D138" s="6" t="inlineStr">
@@ -13499,7 +13499,7 @@
       </c>
       <c r="S138" s="4" t="inlineStr">
         <is>
-          <t>人们期待它能成为唯一能够飞到宇宙的宝可梦，然而至今也努力未果。</t>
+          <t>人們期待它能成為唯一能夠飛到宇宙的寶可夢，然而至今也努力未果。</t>
         </is>
       </c>
     </row>
@@ -13509,7 +13509,7 @@
       </c>
       <c r="C139" s="6" t="inlineStr">
         <is>
-          <t>菊石兽</t>
+          <t>菊石獸</t>
         </is>
       </c>
       <c r="D139" s="6" t="inlineStr">
@@ -13587,7 +13587,7 @@
       </c>
       <c r="S139" s="4" t="inlineStr">
         <is>
-          <t>用化石复原出的宝可梦，靠巧妙地弯曲它的10条腿在古代的大海里飘荡。</t>
+          <t>用化石復原出的寶可夢，靠巧妙地彎曲它的10條腿在古代的大海裡飄蕩。</t>
         </is>
       </c>
     </row>
@@ -13597,7 +13597,7 @@
       </c>
       <c r="C140" s="6" t="inlineStr">
         <is>
-          <t>多刺菊石兽</t>
+          <t>多刺菊石獸</t>
         </is>
       </c>
       <c r="D140" s="6" t="inlineStr">
@@ -13675,7 +13675,7 @@
       </c>
       <c r="S140" s="4" t="inlineStr">
         <is>
-          <t>它拥有锋利的牙齿，但据说它由于外壳过大，不易移动而导致灭绝。</t>
+          <t>它擁有鋒利的牙齒，但據說它由於外殼過大，不易移動而導致滅絕。</t>
         </is>
       </c>
     </row>
@@ -13763,7 +13763,7 @@
       </c>
       <c r="S141" s="4" t="inlineStr">
         <is>
-          <t>由化石复活而成的宝可梦。在藏匿于海底时似乎会用背上的眼睛观察周围的情况。</t>
+          <t>由化石復活而成的寶可夢。在藏匿於海底時似乎會用背上的眼睛觀察周圍的情況。</t>
         </is>
       </c>
     </row>
@@ -13773,7 +13773,7 @@
       </c>
       <c r="C142" s="6" t="inlineStr">
         <is>
-          <t>镰刀盔</t>
+          <t>鐮刀盔</t>
         </is>
       </c>
       <c r="D142" s="6" t="inlineStr">
@@ -13851,7 +13851,7 @@
       </c>
       <c r="S142" s="4" t="inlineStr">
         <is>
-          <t>用纤细的身体快速游动。似乎会用镰刀撕裂猎物吸取体液。</t>
+          <t>用纖細的身體快速遊動。似乎會用鐮刀撕裂獵物吸取體液。</t>
         </is>
       </c>
     </row>
@@ -13861,7 +13861,7 @@
       </c>
       <c r="C143" s="6" t="inlineStr">
         <is>
-          <t>化石翼龙</t>
+          <t>化石翼龍</t>
         </is>
       </c>
       <c r="D143" s="6" t="inlineStr">
@@ -13939,7 +13939,7 @@
       </c>
       <c r="S143" s="4" t="inlineStr">
         <is>
-          <t>通过研究从琥珀中提取出来的基因复活而成，是远古时期的凶恶宝可梦。</t>
+          <t>藉由研究從琥珀中提取出來的基因復活而成，是遠古時期的兇惡寶可夢。</t>
         </is>
       </c>
     </row>
@@ -13949,7 +13949,7 @@
       </c>
       <c r="C144" s="6" t="inlineStr">
         <is>
-          <t>卡比兽</t>
+          <t>卡比獸</t>
         </is>
       </c>
       <c r="D144" s="6" t="inlineStr">
@@ -14027,7 +14027,7 @@
       </c>
       <c r="S144" s="4" t="inlineStr">
         <is>
-          <t>就算是有些发霉的食物也能毫不在意地吃完，并且完全不会吃坏肚子。</t>
+          <t>就算是有些發黴的食物也能毫不在意地吃完，並且完全不會吃壞肚子。</t>
         </is>
       </c>
     </row>
@@ -14037,7 +14037,7 @@
       </c>
       <c r="C145" s="6" t="inlineStr">
         <is>
-          <t>急冻鸟</t>
+          <t>急凍鳥</t>
         </is>
       </c>
       <c r="D145" s="6" t="inlineStr">
@@ -14115,7 +14115,7 @@
       </c>
       <c r="S145" s="4" t="inlineStr">
         <is>
-          <t>传说的鸟宝可梦。它能将冬日空中的空气中含有的水分冻结，降下雪花。</t>
+          <t>傳說的鳥寶可夢。它能將冬日空中的空氣中含有的水分凍結，降下雪花。</t>
         </is>
       </c>
     </row>
@@ -14125,7 +14125,7 @@
       </c>
       <c r="C146" s="6" t="inlineStr">
         <is>
-          <t>闪电鸟</t>
+          <t>閃電鳥</t>
         </is>
       </c>
       <c r="D146" s="6" t="inlineStr">
@@ -14203,7 +14203,7 @@
       </c>
       <c r="S146" s="4" t="inlineStr">
         <is>
-          <t>当天空黑暗，落雷不断时，这只传说的宝可梦就会出现。</t>
+          <t>當天空黑暗，落雷不斷時，這隻傳說的寶可夢就會出現。</t>
         </is>
       </c>
     </row>
@@ -14213,7 +14213,7 @@
       </c>
       <c r="C147" s="6" t="inlineStr">
         <is>
-          <t>火焰鸟</t>
+          <t>火焰鳥</t>
         </is>
       </c>
       <c r="D147" s="6" t="inlineStr">
@@ -14291,7 +14291,7 @@
       </c>
       <c r="S147" s="4" t="inlineStr">
         <is>
-          <t>传说的鸟宝可梦。当它挥舞起剧烈燃烧着的双翅，哪怕是夜空也会被点亮。</t>
+          <t>傳說的鳥寶可夢。當它揮舞起劇烈燃燒著的雙翅，哪怕是夜空也會被點亮。</t>
         </is>
       </c>
     </row>
@@ -14301,7 +14301,7 @@
       </c>
       <c r="C148" s="6" t="inlineStr">
         <is>
-          <t>迷你龙</t>
+          <t>迷你龍</t>
         </is>
       </c>
       <c r="D148" s="6" t="inlineStr">
@@ -14379,7 +14379,7 @@
       </c>
       <c r="S148" s="18" t="inlineStr">
         <is>
-          <t>原本被认为只存在于幻想之中，直到最近有人将它钓起，它的存在才得到了证实。</t>
+          <t>原本被認為只存在於幻想之中，直到最近有人將它釣起，它的存在才得到了證實。</t>
         </is>
       </c>
     </row>
@@ -14389,7 +14389,7 @@
       </c>
       <c r="C149" s="6" t="inlineStr">
         <is>
-          <t>哈克龙</t>
+          <t>哈克龍</t>
         </is>
       </c>
       <c r="D149" s="6" t="inlineStr">
@@ -14467,7 +14467,7 @@
       </c>
       <c r="S149" s="4" t="inlineStr">
         <is>
-          <t>根据目击者的描述，哈克龙的身上散发着一种神秘的气场。</t>
+          <t>根據目擊者的描述，哈克龍的身上散發著一種神秘的氣場。</t>
         </is>
       </c>
     </row>
@@ -14477,7 +14477,7 @@
       </c>
       <c r="C150" s="6" t="inlineStr">
         <is>
-          <t>快龙</t>
+          <t>快龍</t>
         </is>
       </c>
       <c r="D150" s="6" t="inlineStr">
@@ -14555,7 +14555,7 @@
       </c>
       <c r="S150" s="4" t="inlineStr">
         <is>
-          <t>据说它生活在无垠大海的某个地方，靠飞行来移动。但这也只是一个传言罢了。</t>
+          <t>據說它生活在無垠大海的某個地方，靠飛行來移動。但這也只是一個傳言罷了。</t>
         </is>
       </c>
     </row>
@@ -14565,7 +14565,7 @@
       </c>
       <c r="C151" s="6" t="inlineStr">
         <is>
-          <t>超梦</t>
+          <t>超夢</t>
         </is>
       </c>
       <c r="D151" s="6" t="inlineStr">
@@ -14643,7 +14643,7 @@
       </c>
       <c r="S151" s="4" t="inlineStr">
         <is>
-          <t>超梦的基因几乎和梦幻完全一样，但是大小和性格却迥异得让人吃惊。</t>
+          <t>超夢的基因幾乎和夢幻完全一樣，但是大小和性格卻迥異得讓人吃驚。</t>
         </is>
       </c>
     </row>
@@ -14653,7 +14653,7 @@
       </c>
       <c r="C152" s="10" t="inlineStr">
         <is>
-          <t>梦幻</t>
+          <t>夢幻</t>
         </is>
       </c>
       <c r="D152" s="10" t="inlineStr">
@@ -14731,7 +14731,7 @@
       </c>
       <c r="S152" s="4" t="inlineStr">
         <is>
-          <t>用显微镜可以看到它身上极短极细且密集的体毛。</t>
+          <t>用顯微鏡可以看到它身上極短極細且密集的體毛。</t>
         </is>
       </c>
     </row>
@@ -14741,7 +14741,7 @@
       </c>
       <c r="C153" s="13" t="inlineStr">
         <is>
-          <t>缺失编号</t>
+          <t>缺失編號</t>
         </is>
       </c>
       <c r="D153" s="13" t="inlineStr">
